--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -3362,7 +3362,7 @@
         <v>122799497</v>
       </c>
       <c r="B26" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>125552766</v>
       </c>
       <c r="B27" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -3388,11 +3388,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
@@ -3513,11 +3509,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -3362,7 +3362,7 @@
         <v>122799497</v>
       </c>
       <c r="B26" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>125552766</v>
       </c>
       <c r="B27" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
